--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0159.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0159.xlsx
@@ -32751,7 +32751,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Này! Để ta phá tảng đá này!</t>
+          <t>Này! Để tao phá tảng đá này!</t>
         </is>
       </c>
     </row>
